--- a/diseases/d162/1990-1994.xlsx
+++ b/diseases/d162/1990-1994.xlsx
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25149,7 +25149,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25949,7 +25949,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -34667,7 +34667,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -37017,7 +37017,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39017,7 +39017,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39417,7 +39417,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39817,7 +39817,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40617,7 +40617,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -48525,7 +48525,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -50875,7 +50875,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51675,7 +51675,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52075,7 +52075,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52475,7 +52475,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52875,7 +52875,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53275,7 +53275,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53675,7 +53675,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54075,7 +54075,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54475,7 +54475,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54875,7 +54875,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -62383,7 +62383,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -64733,7 +64733,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -65133,7 +65133,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65533,7 +65533,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -65933,7 +65933,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -66333,7 +66333,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -66733,7 +66733,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -67133,7 +67133,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -67533,7 +67533,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -67933,7 +67933,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -68333,7 +68333,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -68733,7 +68733,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">

--- a/diseases/d162/1990-1994.xlsx
+++ b/diseases/d162/1990-1994.xlsx
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25149,7 +25149,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25949,7 +25949,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -34667,7 +34667,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -37017,7 +37017,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37817,7 +37817,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38217,7 +38217,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39017,7 +39017,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39417,7 +39417,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39817,7 +39817,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40617,7 +40617,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -48525,7 +48525,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -50875,7 +50875,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51275,7 +51275,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51675,7 +51675,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52075,7 +52075,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52475,7 +52475,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52875,7 +52875,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53275,7 +53275,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53675,7 +53675,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54075,7 +54075,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54475,7 +54475,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -54875,7 +54875,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -62383,7 +62383,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -64733,7 +64733,7 @@
       </c>
       <c r="AM325" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN325" t="b">
@@ -65133,7 +65133,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -65533,7 +65533,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -65933,7 +65933,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -66333,7 +66333,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -66733,7 +66733,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -67133,7 +67133,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -67533,7 +67533,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -67933,7 +67933,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -68333,7 +68333,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -68733,7 +68733,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">
